--- a/artfynd/A 14520-2024 artfynd.xlsx
+++ b/artfynd/A 14520-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104185629</v>
+        <v>104185643</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fröjnäsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646847.6768711263</v>
+        <v>646869</v>
       </c>
       <c r="R2" t="n">
-        <v>7237283.653346308</v>
+        <v>7237344</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +743,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104185643</v>
+        <v>104185634</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646868.6499523736</v>
+        <v>646867</v>
       </c>
       <c r="R3" t="n">
-        <v>7237343.942076395</v>
+        <v>7237352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +840,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,50 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104185634</v>
+        <v>104185629</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fröjnäsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646866.5745721266</v>
+        <v>646848</v>
       </c>
       <c r="R4" t="n">
-        <v>7237351.821704104</v>
+        <v>7237284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,19 +941,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
